--- a/testcases/Summary_Report_Dolibarr_v2.xlsx
+++ b/testcases/Summary_Report_Dolibarr_v2.xlsx
@@ -133,7 +133,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -155,55 +155,11 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -280,8 +236,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -726,9 +680,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1062,9 +1013,9 @@
           <t>Document Control information</t>
         </is>
       </c>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="31" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
@@ -1077,8 +1028,8 @@
           <t>Faculty of Information Technology — HUFLIT</t>
         </is>
       </c>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="31" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="6" t="inlineStr">
@@ -1091,8 +1042,8 @@
           <t>19-Oct-2026</t>
         </is>
       </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="31" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
@@ -1105,8 +1056,8 @@
           <t>Đặng Hải Phi (23DH112608)</t>
         </is>
       </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="31" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
@@ -1119,8 +1070,8 @@
           <t>Đồ án thực tập — nội bộ</t>
         </is>
       </c>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="31" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
@@ -1128,9 +1079,9 @@
           <t>Document Revision History</t>
         </is>
       </c>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="31" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="B12" s="9" t="inlineStr">
@@ -1222,9 +1173,9 @@
           <t>Project Information</t>
         </is>
       </c>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="31" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="6" t="inlineStr">
@@ -1237,8 +1188,8 @@
           <t>Kiểm thử phần mềm Dolibarr ERP &amp; CRM 22.0.4</t>
         </is>
       </c>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="31" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
     </row>
     <row r="6" ht="35" customHeight="1">
       <c r="B6" s="6" t="inlineStr">
@@ -1251,8 +1202,8 @@
           <t>Đồ án thực tập — kiểm thử Dolibarr ERP &amp; CRM 22.0.4 trên 3 module CRM, Sales &amp; Invoicing, Stock. Tổng 100 test case: 57 Automation (Selenium C# + MSTest, POM) và 43 Manual.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="31" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="6" t="inlineStr">
@@ -1265,8 +1216,8 @@
           <t>19-Oct-2026</t>
         </is>
       </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="31" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
@@ -1279,8 +1230,8 @@
           <t>Đặng Hải Phi (23DH112608)</t>
         </is>
       </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="31" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="B9" s="9" t="inlineStr">
@@ -1391,6 +1342,18 @@
           <t>TEST SUMMARY REPORT — Dolibarr ERP &amp; CRM 22.0.4</t>
         </is>
       </c>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="16" t="n"/>
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="16" t="n"/>
+      <c r="K2" s="16" t="n"/>
+      <c r="L2" s="16" t="n"/>
+      <c r="M2" s="16" t="n"/>
+      <c r="N2" s="16" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="B4" s="4" t="inlineStr">
@@ -1398,18 +1361,18 @@
           <t>OVERALL INFORMATION</t>
         </is>
       </c>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="31" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="6" t="inlineStr">
@@ -1422,17 +1385,17 @@
           <t>Đánh giá chất lượng chức năng Dolibarr ERP &amp; CRM 22.0.4 (CRM, Sales &amp; Invoicing, Stock) bằng kiểm thử tự động (Selenium C# + MSTest, POM) và kiểm thử thủ công.</t>
         </is>
       </c>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="31" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
@@ -1445,17 +1408,17 @@
           <t>1 (Đặng Hải Phi)</t>
         </is>
       </c>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="31" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
@@ -1463,18 +1426,18 @@
           <t>OVERALL STATUS</t>
         </is>
       </c>
-      <c r="C8" s="30" t="n"/>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="30" t="n"/>
-      <c r="F8" s="30" t="n"/>
-      <c r="G8" s="30" t="n"/>
-      <c r="H8" s="30" t="n"/>
-      <c r="I8" s="30" t="n"/>
-      <c r="J8" s="30" t="n"/>
-      <c r="K8" s="30" t="n"/>
-      <c r="L8" s="30" t="n"/>
-      <c r="M8" s="30" t="n"/>
-      <c r="N8" s="31" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
@@ -1491,8 +1454,8 @@
           <t>Number of Defects</t>
         </is>
       </c>
-      <c r="F9" s="30" t="n"/>
-      <c r="G9" s="31" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
       <c r="H9" s="17">
         <f>COUNTA('2. Defects Report'!$D:$D)-1</f>
         <v/>
@@ -1513,8 +1476,8 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="31" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
       <c r="H10" s="17">
         <f>COUNTIF('2. Defects Report'!$L:$L,"Critical")</f>
         <v/>
@@ -1535,8 +1498,8 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="31" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
       <c r="H11" s="17">
         <f>COUNTIF('2. Defects Report'!$L:$L,"High")</f>
         <v/>
@@ -1557,8 +1520,8 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="31" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
       <c r="H12" s="17">
         <f>COUNTIF('2. Defects Report'!$L:$L,"Medium")</f>
         <v/>
@@ -1579,8 +1542,8 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="31" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
       <c r="H13" s="17">
         <f>COUNTIF('2. Defects Report'!$L:$L,"Minor")</f>
         <v/>
@@ -1601,8 +1564,8 @@
           <t>Status: New (chưa xử lý)</t>
         </is>
       </c>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="31" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
       <c r="H14" s="17">
         <f>COUNTIF('2. Defects Report'!$M:$M,"New")</f>
         <v/>
@@ -1623,8 +1586,8 @@
           <t>Status: Fixed</t>
         </is>
       </c>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="31" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
       <c r="H15" s="17">
         <f>COUNTIF('2. Defects Report'!$M:$M,"Fixed")</f>
         <v/>
@@ -2323,8 +2286,10 @@
         <f>SUM(J19:J28)</f>
         <v/>
       </c>
-      <c r="K29" s="24" t="n">
-        <v>4258</v>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L29" s="24">
         <f>SUM(L19:L28)</f>
@@ -2334,11 +2299,7 @@
         <f>IFERROR(L29/J29,0)</f>
         <v/>
       </c>
-      <c r="N29" s="23" t="inlineStr">
-        <is>
-          <t>4.258 dòng code C# (bỏ trống &amp; comment) đo trên 27 files POM &amp; Test Methods.</t>
-        </is>
-      </c>
+      <c r="N29" s="23" t="inlineStr"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="B31" s="4" t="inlineStr">
@@ -2346,18 +2307,18 @@
           <t>CHARTS</t>
         </is>
       </c>
-      <c r="C31" s="30" t="n"/>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="30" t="n"/>
-      <c r="F31" s="30" t="n"/>
-      <c r="G31" s="30" t="n"/>
-      <c r="H31" s="30" t="n"/>
-      <c r="I31" s="30" t="n"/>
-      <c r="J31" s="30" t="n"/>
-      <c r="K31" s="30" t="n"/>
-      <c r="L31" s="30" t="n"/>
-      <c r="M31" s="30" t="n"/>
-      <c r="N31" s="31" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="B50" s="27" t="inlineStr">
@@ -2423,6 +2384,21 @@
           <t>DEFECTS REPORT</t>
         </is>
       </c>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="16" t="n"/>
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="16" t="n"/>
+      <c r="K2" s="16" t="n"/>
+      <c r="L2" s="16" t="n"/>
+      <c r="M2" s="16" t="n"/>
+      <c r="N2" s="16" t="n"/>
+      <c r="O2" s="16" t="n"/>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="16" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="B4" s="9" t="inlineStr">
@@ -2618,6 +2594,8 @@
           <t>EVIDENCE — Minh chứng kiểm thử</t>
         </is>
       </c>
+      <c r="C1" s="16" t="n"/>
+      <c r="D1" s="16" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="B3" s="9" t="inlineStr">
